--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,12 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501064.6880456261</v>
+        <v>501065</v>
       </c>
       <c r="R3" t="n">
-        <v>6251506.909513642</v>
+        <v>6251507</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -884,19 +879,9 @@
           <t>1985-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1985-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105609</v>
+        <v>105621</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105621</v>
+        <v>105630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105630</v>
+        <v>105642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17339-2025 artfynd.xlsx
+++ b/artfynd/A 17339-2025 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>80351489</v>
       </c>
       <c r="B3" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
